--- a/bom/jeon_history.xlsx
+++ b/bom/jeon_history.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -88,6 +88,11 @@
     </font>
     <font>
       <name val="Malgun Gothic"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Dotum"/>
       <color rgb="FF808080"/>
       <sz val="11"/>
     </font>
@@ -167,7 +172,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -274,6 +279,20 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="27.4" customWidth="1" style="15" min="1" max="1"/>
@@ -1282,200 +1301,291 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>NESPRESSO_스타필드하남</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>NESPRESSO</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>스타필드 하남 1F</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>매장(카페)</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="15" t="n">
         <v>95.59999999999999</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>소규모</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>단층(1F)</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="15" t="n">
         <v>41</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="15" t="n">
         <v>510</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="15" t="n">
         <v>595</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="15" t="n">
         <v>67</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8" s="15" t="n">
         <v>5.33</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="15" t="n">
         <v>6.22</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="15" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t>1F 전체 (전력간선+전열+전등+집기조명+통신+CCTV+방송+소방+로고)</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>NESPRESSO_스타필드하남_물량산출_20260406.xlsx</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" s="15" t="inlineStr">
         <is>
           <t>NESPRESSO_스타필드하남</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" s="15" t="inlineStr">
         <is>
           <t>단독</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" s="15" t="inlineStr">
         <is>
           <t>2026-04-06T20:09:00</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="V8" s="15" t="inlineStr">
         <is>
           <t>v3.3-auto</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="W8" s="15" t="inlineStr">
         <is>
           <t>PDF(CAD출력본) 15p, E-001~E-015, 스케일1/50, SMPS BOX 포함, 자동산출</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>FIVEGUYS_더갤러리아7호점</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>FIVE GUYS</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>the Galleria 더갤러리아</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>F&amp;B/레스토랑</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="15" t="n">
         <v>400.2</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>중규모</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>B1F~2F</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="15" t="n">
         <v>1650</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="15" t="n">
         <v>35</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="15" t="n">
         <v>80</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="15" t="n">
         <v>4.12</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="15" t="inlineStr">
         <is>
           <t>1/1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="15" t="inlineStr">
         <is>
           <t>B1F~2F 전체 (전력간선+동력+전열+전등+통신+CCTV+방송)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="15" t="inlineStr">
         <is>
           <t>FIVEGUYS_더갤러리아7호점_물량산출_20260406.xlsx</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" s="15" t="inlineStr">
         <is>
           <t>FIVEGUYS_더갤러리아7호점</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T9" s="15" t="inlineStr">
         <is>
           <t>단독</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" s="15" t="inlineStr">
         <is>
           <t>2026-04-06T20:13:00</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V9" s="15" t="inlineStr">
         <is>
           <t>v3.3-auto</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="W9" s="15" t="inlineStr">
         <is>
           <t>PDF(준공도면) 40p, E-001~E-112+ET-001~ET-201, 스케일1/50(A1), 주방장비 K1-K18 포함, 자동산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>까르띠에_매장</t>
+        </is>
+      </c>
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>까르띠에(Cartier)</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="38" t="inlineStr">
+        <is>
+          <t>소규모</t>
+        </is>
+      </c>
+      <c r="G10" s="38" t="inlineStr">
+        <is>
+          <t>단층(1F)</t>
+        </is>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="J10" s="41" t="n">
+        <v>274.3</v>
+      </c>
+      <c r="K10" s="41" t="n">
+        <v>286.7</v>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="N10" s="42" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O10" s="42" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P10" s="38" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="Q10" s="38" t="inlineStr">
+        <is>
+          <t>1F 전체 (러프모드)</t>
+        </is>
+      </c>
+      <c r="R10" s="38" t="inlineStr">
+        <is>
+          <t>까르띠에_매장_물량산출_20260406.xlsx</t>
+        </is>
+      </c>
+      <c r="S10" s="38" t="inlineStr">
+        <is>
+          <t>까르띠에_매장</t>
+        </is>
+      </c>
+      <c r="T10" s="43" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="U10" s="38" t="inlineStr">
+        <is>
+          <t>2026-04-06T20:10:00</t>
+        </is>
+      </c>
+      <c r="V10" s="38" t="inlineStr">
+        <is>
+          <t>v3.3-auto</t>
+        </is>
+      </c>
+      <c r="W10" s="39" t="inlineStr">
+        <is>
+          <t>러프모드 산출 (판넬설명서만 존재, CAD 평면도 없음, 면적 100㎡ 추정)</t>
         </is>
       </c>
     </row>

--- a/bom/jeon_history.xlsx
+++ b/bom/jeon_history.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -96,6 +96,15 @@
       <color rgb="FF808080"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="돋움"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="돋움"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -172,7 +181,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -291,6 +300,27 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -587,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="27.4" customWidth="1" style="15" min="1" max="1"/>
@@ -1589,6 +1619,105 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>FIVEGUYS_더갤러리아7호점</t>
+        </is>
+      </c>
+      <c r="B11" s="44" t="inlineStr">
+        <is>
+          <t>FIVE GUYS</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="inlineStr">
+        <is>
+          <t>the Galleria 더갤러리아</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="inlineStr">
+        <is>
+          <t>F&amp;B/레스토랑</t>
+        </is>
+      </c>
+      <c r="E11" s="46" t="n">
+        <v>400.2</v>
+      </c>
+      <c r="F11" s="47" t="inlineStr">
+        <is>
+          <t>대규모</t>
+        </is>
+      </c>
+      <c r="G11" s="44" t="inlineStr">
+        <is>
+          <t>B1F~2F</t>
+        </is>
+      </c>
+      <c r="H11" s="46" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" s="46" t="n">
+        <v>85</v>
+      </c>
+      <c r="J11" s="48" t="n">
+        <v>1530.3</v>
+      </c>
+      <c r="K11" s="48" t="n">
+        <v>5149</v>
+      </c>
+      <c r="L11" s="46" t="n">
+        <v>14</v>
+      </c>
+      <c r="M11" s="46" t="n">
+        <v>22</v>
+      </c>
+      <c r="N11" s="49" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="O11" s="49" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="P11" s="47" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="Q11" s="44" t="inlineStr">
+        <is>
+          <t>B1F~2F 전체 (LP-1M 53회로+LP-E 19회로+LP-2M 20회로+온수기6+간선4)</t>
+        </is>
+      </c>
+      <c r="R11" s="44" t="inlineStr">
+        <is>
+          <t>파이브가이즈_7호점_도면인덱스_20260408.xlsx</t>
+        </is>
+      </c>
+      <c r="S11" s="44" t="inlineStr">
+        <is>
+          <t>FIVEGUYS_더갤러리아7호점</t>
+        </is>
+      </c>
+      <c r="T11" s="50" t="inlineStr">
+        <is>
+          <t>단독</t>
+        </is>
+      </c>
+      <c r="U11" s="44" t="inlineStr">
+        <is>
+          <t>2026-04-08T16:10:45</t>
+        </is>
+      </c>
+      <c r="V11" s="47" t="inlineStr">
+        <is>
+          <t>v3.2-harness</t>
+        </is>
+      </c>
+      <c r="W11" s="45" t="inlineStr">
+        <is>
+          <t>PDF 준공도면 40p A3 1/100 · LP-1M 2열 전수재추출 완료 · SMPS 2차측 L1/L2 계상 · KEC 검증 ✅ · 레벨A PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W1"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
